--- a/public/coffee/bar.xlsx
+++ b/public/coffee/bar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/coffee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8058F9-42E4-4345-B337-8931CC971F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C090EA7-1998-9C43-A118-EF9F0C7171F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="5180" windowWidth="22500" windowHeight="11740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5240" yWindow="5120" windowWidth="22500" windowHeight="11740" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="249">
   <si>
     <t>name_ru</t>
   </si>
@@ -780,15 +780,6 @@
     <t>ბელინი</t>
   </si>
   <si>
-    <t>МонБлан</t>
-  </si>
-  <si>
-    <t>monc blanc</t>
-  </si>
-  <si>
-    <t>მონ ბლან</t>
-  </si>
-  <si>
     <t>Клюквенный колд брю</t>
   </si>
   <si>
@@ -796,15 +787,6 @@
   </si>
   <si>
     <t>ცივი ყავის ფილტრი შტოშის</t>
-  </si>
-  <si>
-    <t>Кремовый матча оранж</t>
-  </si>
-  <si>
-    <t>matcha orange creamy</t>
-  </si>
-  <si>
-    <t>ფორთოხლის მატჩა ნაღებით</t>
   </si>
 </sst>
 </file>
@@ -5505,7 +5487,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA998"/>
+  <dimension ref="A1:AA997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
@@ -5577,11 +5559,11 @@
         <v>74</v>
       </c>
       <c r="I2" s="13" t="str">
-        <f t="shared" ref="I2:I11" si="0">LOWER($B2)</f>
+        <f t="shared" ref="I2:I10" si="0">LOWER($B2)</f>
         <v>filter coffee</v>
       </c>
       <c r="J2" s="13" t="str">
-        <f t="shared" ref="J2:J11" si="1">LOWER($B2)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J2:J10" si="1">LOWER($B2)&amp;"_"&amp;2</f>
         <v>filter coffee_2</v>
       </c>
       <c r="K2" s="6"/>
@@ -5924,18 +5906,18 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="22">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="13" t="str">
         <f t="shared" si="0"/>
-        <v>monc blanc</v>
+        <v>cold brew cranberry</v>
       </c>
       <c r="J10" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>monc blanc_2</v>
+        <v>cold brew cranberry_2</v>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
@@ -5956,30 +5938,16 @@
       <c r="AA10" s="6"/>
     </row>
     <row r="11" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A11" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22">
-        <v>12</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>cold brew cranberry</v>
-      </c>
-      <c r="J11" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>cold brew cranberry_2</v>
-      </c>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -6955,7 +6923,7 @@
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
     </row>
-    <row r="45" spans="1:27" ht="15.75" customHeight="1">
+    <row r="45" spans="1:27" ht="13">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -34591,35 +34559,6 @@
       <c r="Y997" s="6"/>
       <c r="Z997" s="6"/>
       <c r="AA997" s="6"/>
-    </row>
-    <row r="998" spans="1:27" ht="13">
-      <c r="A998" s="6"/>
-      <c r="B998" s="6"/>
-      <c r="C998" s="6"/>
-      <c r="D998" s="18"/>
-      <c r="E998" s="18"/>
-      <c r="F998" s="6"/>
-      <c r="G998" s="6"/>
-      <c r="H998" s="6"/>
-      <c r="I998" s="6"/>
-      <c r="J998" s="6"/>
-      <c r="K998" s="6"/>
-      <c r="L998" s="6"/>
-      <c r="M998" s="6"/>
-      <c r="N998" s="6"/>
-      <c r="O998" s="6"/>
-      <c r="P998" s="6"/>
-      <c r="Q998" s="6"/>
-      <c r="R998" s="6"/>
-      <c r="S998" s="6"/>
-      <c r="T998" s="6"/>
-      <c r="U998" s="6"/>
-      <c r="V998" s="6"/>
-      <c r="W998" s="6"/>
-      <c r="X998" s="6"/>
-      <c r="Y998" s="6"/>
-      <c r="Z998" s="6"/>
-      <c r="AA998" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -63661,7 +63600,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:27" ht="15">
@@ -63725,11 +63664,11 @@
         <v>158</v>
       </c>
       <c r="I2" s="13" t="str">
-        <f t="shared" ref="I2:I7" si="0">LOWER($B2)</f>
+        <f t="shared" ref="I2:I6" si="0">LOWER($B2)</f>
         <v>matcha-ice matcha</v>
       </c>
       <c r="J2" s="13" t="str">
-        <f t="shared" ref="J2:J7" si="1">LOWER($B2)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J2:J6" si="1">LOWER($B2)&amp;"_"&amp;2</f>
         <v>matcha-ice matcha_2</v>
       </c>
       <c r="K2" s="6"/>
@@ -63914,49 +63853,6 @@
         <v>matcha colada_2</v>
       </c>
       <c r="AA6" s="6"/>
-    </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A7" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22">
-        <v>15</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>matcha orange creamy</v>
-      </c>
-      <c r="J7" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>matcha orange creamy_2</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/coffee/bar.xlsx
+++ b/public/coffee/bar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/coffee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C090EA7-1998-9C43-A118-EF9F0C7171F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D4F9C-EAE5-6743-A153-65CE4882754A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="5120" windowWidth="22500" windowHeight="11740" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5240" yWindow="5120" windowWidth="22500" windowHeight="11740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="249">
   <si>
     <t>name_ru</t>
   </si>
@@ -34739,9 +34739,7 @@
       <c r="C4" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>62</v>
-      </c>
+      <c r="D4" s="18"/>
       <c r="E4" s="18" t="s">
         <v>224</v>
       </c>
@@ -34790,9 +34788,7 @@
       <c r="C5" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>62</v>
-      </c>
+      <c r="D5" s="18"/>
       <c r="E5" s="18" t="s">
         <v>97</v>
       </c>
@@ -34841,9 +34837,7 @@
       <c r="C6" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="5">
-        <v>350</v>
-      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="5">
         <v>12</v>
       </c>
@@ -34875,9 +34869,7 @@
       <c r="C7" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="5">
-        <v>350</v>
-      </c>
+      <c r="D7" s="5"/>
       <c r="E7" s="5">
         <v>12</v>
       </c>
@@ -34909,9 +34901,7 @@
       <c r="C8" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D8" s="5">
-        <v>350</v>
-      </c>
+      <c r="D8" s="5"/>
       <c r="E8" s="5">
         <v>12</v>
       </c>
@@ -34943,9 +34933,7 @@
       <c r="C9" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D9" s="5">
-        <v>350</v>
-      </c>
+      <c r="D9" s="5"/>
       <c r="E9" s="5">
         <v>12</v>
       </c>
@@ -63648,9 +63636,7 @@
       <c r="C2" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="D2" s="17"/>
       <c r="E2" s="17" t="s">
         <v>63</v>
       </c>
@@ -63699,9 +63685,7 @@
       <c r="C3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>41</v>
-      </c>
+      <c r="D3" s="17"/>
       <c r="E3" s="17" t="s">
         <v>97</v>
       </c>
@@ -63743,9 +63727,7 @@
       <c r="C4" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>41</v>
-      </c>
+      <c r="D4" s="17"/>
       <c r="E4" s="17" t="s">
         <v>97</v>
       </c>
@@ -63794,9 +63776,7 @@
       <c r="C5" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="5">
-        <v>250</v>
-      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="5">
         <v>15</v>
       </c>
@@ -63829,9 +63809,7 @@
       <c r="C6" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D6" s="5">
-        <v>250</v>
-      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="5">
         <v>15</v>
       </c>

--- a/public/coffee/bar.xlsx
+++ b/public/coffee/bar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/coffee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D4F9C-EAE5-6743-A153-65CE4882754A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8599605A-DC27-164D-B2AE-A92EC0B0BEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="5120" windowWidth="22500" windowHeight="11740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3460" windowWidth="22500" windowHeight="11740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="253">
   <si>
     <t>name_ru</t>
   </si>
@@ -788,6 +788,18 @@
   <si>
     <t>ცივი ყავის ფილტრი შტოშის</t>
   </si>
+  <si>
+    <t>bumble4</t>
+  </si>
+  <si>
+    <t>bumble4_2</t>
+  </si>
+  <si>
+    <t>V602</t>
+  </si>
+  <si>
+    <t>V602_2</t>
+  </si>
 </sst>
 </file>
 
@@ -5609,13 +5621,11 @@
       <c r="H3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>v60</v>
+      <c r="I3" s="13" t="s">
+        <v>251</v>
       </c>
-      <c r="J3" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>v60_2</v>
+      <c r="J3" s="13" t="s">
+        <v>252</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -34801,13 +34811,11 @@
       <c r="H5" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I5" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>bumble</v>
+      <c r="I5" s="13" t="s">
+        <v>249</v>
       </c>
-      <c r="J5" s="13" t="str">
-        <f t="shared" si="1"/>
-        <v>bumble_2</v>
+      <c r="J5" s="13" t="s">
+        <v>250</v>
       </c>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>

--- a/public/coffee/bar.xlsx
+++ b/public/coffee/bar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/coffee/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8599605A-DC27-164D-B2AE-A92EC0B0BEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE2B188-5C16-844E-9351-27B936BABF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3460" windowWidth="22500" windowHeight="11740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3460" windowWidth="10800" windowHeight="11740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catalogs" sheetId="1" r:id="rId1"/>
@@ -795,10 +795,10 @@
     <t>bumble4_2</t>
   </si>
   <si>
-    <t>V602</t>
+    <t>v601</t>
   </si>
   <si>
-    <t>V602_2</t>
+    <t>v601_2</t>
   </si>
 </sst>
 </file>
@@ -5621,7 +5621,7 @@
       <c r="H3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="16" t="s">
         <v>251</v>
       </c>
       <c r="J3" s="13" t="s">
